--- a/r4-JoanneumResearch-PreNUDGE-AppData-smoking/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-smoking/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:08:27+00:00</t>
+    <t>2026-06-03T12:49:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-smoking/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-smoking/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T12:49:02+00:00</t>
+    <t>2026-06-03T13:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
